--- a/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>发货单号</t>
   </si>
@@ -46,6 +46,9 @@
     <t>单据类型</t>
   </si>
   <si>
+    <t>FBA箱号</t>
+  </si>
+  <si>
     <t>箱号</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
   </si>
   <si>
     <t>{.sourceTypeName}</t>
+  </si>
+  <si>
+    <t>{.fbaBoxNo}</t>
   </si>
   <si>
     <t>{.boxNo}</t>
@@ -1126,31 +1132,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="3" width="21.125" customWidth="1"/>
     <col min="4" max="4" width="19.125" customWidth="1"/>
     <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="16.5" customWidth="1"/>
-    <col min="11" max="11" width="20.5" customWidth="1"/>
-    <col min="12" max="12" width="13.125" customWidth="1"/>
-    <col min="13" max="13" width="12.375" customWidth="1"/>
-    <col min="14" max="14" width="18.5" customWidth="1"/>
-    <col min="15" max="15" width="24.75" customWidth="1"/>
-    <col min="16" max="16" width="14.875" customWidth="1"/>
-    <col min="17" max="17" width="9" customWidth="1"/>
-    <col min="18" max="18" width="36.375" customWidth="1"/>
-    <col min="19" max="19" width="10.375" customWidth="1"/>
-    <col min="21" max="21" width="8.875" customWidth="1"/>
-    <col min="22" max="22" width="31.25" customWidth="1"/>
-    <col min="24" max="24" width="17.375" customWidth="1"/>
-    <col min="26" max="26" width="9.375" customWidth="1"/>
-    <col min="27" max="27" width="18" customWidth="1"/>
+    <col min="6" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="16.5" customWidth="1"/>
+    <col min="12" max="12" width="20.5" customWidth="1"/>
+    <col min="13" max="13" width="13.125" customWidth="1"/>
+    <col min="14" max="14" width="12.375" customWidth="1"/>
+    <col min="15" max="15" width="18.5" customWidth="1"/>
+    <col min="16" max="16" width="24.75" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="36.375" customWidth="1"/>
+    <col min="20" max="20" width="10.375" customWidth="1"/>
+    <col min="22" max="22" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="31.25" customWidth="1"/>
+    <col min="25" max="25" width="17.375" customWidth="1"/>
+    <col min="27" max="27" width="9.375" customWidth="1"/>
+    <col min="28" max="28" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1190,7 +1196,7 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="4" t="s">
@@ -1199,55 +1205,61 @@
       <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:16">
+    <row r="2" s="1" customFormat="1" spans="1:17">
       <c r="A2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>发货单号</t>
   </si>
@@ -55,6 +55,9 @@
     <t>装箱状态</t>
   </si>
   <si>
+    <t>装箱总数量</t>
+  </si>
+  <si>
     <t>平台SKU</t>
   </si>
   <si>
@@ -64,10 +67,16 @@
     <t>装箱SKU</t>
   </si>
   <si>
-    <t>箱子包装重量</t>
-  </si>
-  <si>
-    <t>箱子包装尺寸</t>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>箱子包装重量（kg）</t>
+  </si>
+  <si>
+    <t>箱子包装尺寸长（cm）</t>
+  </si>
+  <si>
+    <t>箱子包装尺寸宽（cm）</t>
   </si>
   <si>
     <t>称重状态</t>
@@ -106,6 +115,9 @@
     <t>{.packingTotalStatusName}</t>
   </si>
   <si>
+    <t>{.totalQty}</t>
+  </si>
+  <si>
     <t>{.platformSku}</t>
   </si>
   <si>
@@ -115,10 +127,19 @@
     <t>{.sku}</t>
   </si>
   <si>
+    <t>{.packQty}</t>
+  </si>
+  <si>
     <t>{.packageWeightStr}</t>
   </si>
   <si>
-    <t>{.boxSize}</t>
+    <t>{.length}</t>
+  </si>
+  <si>
+    <t>{.width}</t>
+  </si>
+  <si>
+    <t>{.height}</t>
   </si>
   <si>
     <t>{.weightingStatusName}</t>
@@ -1132,31 +1153,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="3" width="21.125" customWidth="1"/>
     <col min="4" max="4" width="19.125" customWidth="1"/>
     <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="16.5" customWidth="1"/>
-    <col min="12" max="12" width="20.5" customWidth="1"/>
-    <col min="13" max="13" width="13.125" customWidth="1"/>
-    <col min="14" max="14" width="12.375" customWidth="1"/>
-    <col min="15" max="15" width="18.5" customWidth="1"/>
-    <col min="16" max="16" width="24.75" customWidth="1"/>
-    <col min="17" max="17" width="14.875" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
-    <col min="19" max="19" width="36.375" customWidth="1"/>
-    <col min="20" max="20" width="10.375" customWidth="1"/>
-    <col min="22" max="22" width="8.875" customWidth="1"/>
-    <col min="23" max="23" width="31.25" customWidth="1"/>
-    <col min="25" max="25" width="17.375" customWidth="1"/>
-    <col min="27" max="27" width="9.375" customWidth="1"/>
-    <col min="28" max="28" width="18" customWidth="1"/>
+    <col min="6" max="7" width="18.5" customWidth="1"/>
+    <col min="8" max="8" width="23.125" customWidth="1"/>
+    <col min="9" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="16.5" customWidth="1"/>
+    <col min="13" max="14" width="20.5" customWidth="1"/>
+    <col min="15" max="15" width="21.875" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="19.25" customWidth="1"/>
+    <col min="18" max="18" width="12.375" customWidth="1"/>
+    <col min="19" max="19" width="18.5" customWidth="1"/>
+    <col min="20" max="20" width="24.75" customWidth="1"/>
+    <col min="21" max="21" width="14.875" customWidth="1"/>
+    <col min="22" max="22" width="9" customWidth="1"/>
+    <col min="23" max="23" width="36.375" customWidth="1"/>
+    <col min="24" max="24" width="10.375" customWidth="1"/>
+    <col min="26" max="26" width="8.875" customWidth="1"/>
+    <col min="27" max="27" width="31.25" customWidth="1"/>
+    <col min="29" max="29" width="17.375" customWidth="1"/>
+    <col min="31" max="31" width="9.375" customWidth="1"/>
+    <col min="32" max="32" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1199,67 +1224,91 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="S1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:17">
+    <row r="2" s="1" customFormat="1" spans="1:21">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>发货单号</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>箱子包装尺寸宽（cm）</t>
+  </si>
+  <si>
+    <t>箱子包装尺寸高（cm）</t>
   </si>
   <si>
     <t>称重状态</t>
@@ -1231,84 +1234,84 @@
         <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:21">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>发货单号</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>箱子包装尺寸宽（cm）</t>
+  </si>
+  <si>
+    <t>箱子包装尺寸高（cm）</t>
   </si>
   <si>
     <t>称重状态</t>
@@ -1231,84 +1234,84 @@
         <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:21">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/firstMilePackingDetailExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="50">
   <si>
     <t>发货单号</t>
   </si>
@@ -155,6 +155,18 @@
   </si>
   <si>
     <t>{.measureSourceName}</t>
+  </si>
+  <si>
+    <t>目的仓</t>
+  </si>
+  <si>
+    <t>中转仓</t>
+  </si>
+  <si>
+    <t>{.destWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.transferWarehouseNames}</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1168,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="3" width="21.125" customWidth="1"/>
@@ -1184,7 +1196,7 @@
     <col min="32" max="32" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:23">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1192,64 +1204,70 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:21">
+    <row r="2" s="1" customFormat="1" spans="1:23">
       <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
@@ -1257,60 +1275,66 @@
         <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>41</v>
       </c>
     </row>
